--- a/docs/protocol/Astibot_Floor_Experimental_Test_Protocol_v4.xlsx
+++ b/docs/protocol/Astibot_Floor_Experimental_Test_Protocol_v4.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Straight lane ≥ 11 m: start line, lateral centerline, 8.00 m finish marker (perpendicular line), ≥ 3 m clear run-out after it. Robot reference point: front-bumper centre; two chassis marks (front and rear centre) for alignment.</t>
+          <t>Straight lane ≥ 12 m (same for T1–T3): start line, lateral centerline, 8.00 m finish marker (perpendicular line), ≥ 3 m clear run-out after it. Robot reference point: front-bumper centre; two chassis marks (front and rear centre) for alignment.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -532,12 +532,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Straight lane ≥ 7 m with clear run-out (planned travel 5.5 m at 0.20 m/s², 4.0 m at 0.50, 3.5 m at 1.00; the run aborts 1 m beyond the plan).</t>
+          <t>Same lane as T1 (≥ 12 m): start line, lateral centerline, 8.00 m finish marker, ≥ 3 m clear run-out; same robot reference point and chassis marks.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>a_cmd = 0.20 / 0.50 / 1.00 m/s²; target v = 1.00 m/s; hold 2.0 s; then slow down at 0.50 m/s² (same for every condition).</t>
+          <t>a_cmd = 0.20 / 0.50 / 1.00 m/s²; target v = 1.00 m/s; then as T1: slow down at 0.50 m/s² (same for every condition) and stop when wheel odometry reads 8.00 m. Only the speed-up differs between conditions.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -547,12 +547,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>From full stop at the start line (aligned as T1), the system ramps the speed command at a_cmd (50 Hz) to 1.00 m/s, holds it 2.0 s, slows down at 0.50 m/s² in the remaining lane and holds v = 0 until rest. The robot has no acceleration setting: the ramp is shaped in /cmd_vel, and the recorded /cmd_vel is the actual ramp configuration.</t>
+          <t>As T1 (alignment, logging before motion, robot preparation, independent runs), with the speed-up under test: from full stop the system ramps the speed command at a_cmd (50 Hz) to 1.00 m/s, cruises, slows down at 0.50 m/s² and stops itself at 8.00 m of wheel odometry. The robot has no acceleration setting: the ramp is shaped in /cmd_vel, and the recorded /cmd_vel is the actual ramp configuration. After complete stop, tape Δx and Δy as in T1.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Automatic: acceleration setpoint, target speed, /cmd_vel ramp (50 Hz), reported velocity (/odom_raw), t10/t90 and measured acceleration (wheel speed), IMU ax/ay/az &amp; gyro (bag), mean forward IMU acceleration per phase. Manual: slip-like symptoms.</t>
+          <t>Automatic: acceleration setpoint, target speed, /cmd_vel ramp (50 Hz), reported velocity (/odom_raw), t10/t90 and measured acceleration (wheel speed), IMU ax/ay/az &amp; gyro (bag), mean forward IMU acceleration per phase, odometry endpoint. Manual: Δx, Δy [cm]; slip-like symptoms.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Straight lane ≥ 11 m: start line, trigger mark at 6.00 m (visual reference: the robot triggers on wheel odometry), braking zone and ≥ 4 m clear after the trigger.</t>
+          <t>Same lane as T1 (≥ 12 m): start line, lateral centerline, 8.00 m line, braking zone and ≥ 4 m clear after it; same robot reference point and chassis marks.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>v_initial = 0.20 / 0.50 / 1.00 / 1.50 m/s; approach at 0.50 m/s²; ≥ 1.0 s at steady speed (wheel speed within 5 %) before the trigger; stop mode ACTIVE (v = 0 held).</t>
+          <t>v_initial = 0.20 / 0.50 / 1.00 / 1.50 m/s; as T1 up to the 8.00 m line (accelerate at 0.50 m/s², cruise, ≥ 1.0 s at steady speed: wheel speed within 5 %); at 8.00 m of wheel odometry a sudden stop: v = 0 at once, held (stop mode ACTIVE).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>From the start line (aligned as T1) the system accelerates at 0.50 m/s² to v_initial and cruises; when wheel odometry reads 6.00 m it issues v = 0 (ACTIVE: the motor controllers brake and hold zero) and logs the trigger time and odometry position. After rest, tape the distance from the start line to the reference point (total). Stop distance = total − trigger odometry (computed). COAST (wheel power cut at the trigger) only as a separate, labelled condition. A run not steady at the trigger is flagged (steady_ok = false) and repeated.</t>
+          <t>As T1 (alignment, logging before motion, robot preparation, independent runs) up to the 8.00 m line, without the slow-down: when wheel odometry reads 8.00 m the system issues v = 0 at once (ACTIVE: the motor controllers brake and hold zero) and logs the stop-command time and odometry position. After rest, tape Δx and Δy at the reference point as in T1: Δx is how far past the 8 m line the robot stopped. Stop distance = (8.00 m + Δx) − stop-command odometry (computed). COAST (wheel power cut at the line) only as a separate, labelled condition. A run not steady at the line is flagged (steady_ok = false) and repeated.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Automatic: stop mode, trigger time and odometry, speed at trigger, steady time before the trigger, braking distance (odometry), braking time to 95 % of it, IMU and odometry (bag). Manual: tape start line → reference point at rest [cm].</t>
+          <t>Automatic: stop mode, stop-command time and odometry, speed at the stop command (1 s average), steady time before it, braking distance (odometry), braking time to 95 % of it, wheel power state at rest, IMU and odometry (bag). Manual: Δx, Δy [cm] at the 8 m line.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="2" ht="32.1" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Enter tape measurements for T1 (Δx/Δy at the 8 m line) and T3 (start line → rest; stop distance = that − trigger odometry) • every executed trial logs raw IMU and odometry (bag) • trial ID = &lt;test&gt;_&lt;v|a&gt;&lt;setpoint&gt;_r&lt;repeat&gt;_&lt;HHMMSS&gt;, e.g. T1_v0.50_r3_101530</t>
+          <t>Enter tape measurements for every T1–T3 trial: Δx/Δy at the 8 m line (T3: stop distance = 8 m + Δx − stop-command odometry) • every executed trial logs raw IMU and odometry (bag) • trial ID = &lt;test&gt;_&lt;v|a&gt;&lt;setpoint&gt;_r&lt;repeat&gt;_&lt;HHMMSS&gt;, e.g. T1_v0.50_r3_101530</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Stop distance [cm] (tape total − trigger odometry)</t>
+          <t>Stop distance [cm] (8 m + Δx − stop-command odometry)</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -2054,7 +2054,7 @@
       <c r="J40" s="8" t="n"/>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L40" s="9" t="n"/>
@@ -2092,7 +2092,7 @@
       <c r="J41" s="8" t="n"/>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L41" s="9" t="n"/>
@@ -2130,7 +2130,7 @@
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L42" s="9" t="n"/>
@@ -2168,7 +2168,7 @@
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L43" s="9" t="n"/>
@@ -2206,7 +2206,7 @@
       <c r="J44" s="8" t="n"/>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L44" s="9" t="n"/>
@@ -2244,7 +2244,7 @@
       <c r="J45" s="8" t="n"/>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L45" s="9" t="n"/>
@@ -2282,7 +2282,7 @@
       <c r="J46" s="8" t="n"/>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L46" s="9" t="n"/>
@@ -2320,7 +2320,7 @@
       <c r="J47" s="8" t="n"/>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L47" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
       <c r="J48" s="8" t="n"/>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L48" s="9" t="n"/>
@@ -2396,7 +2396,7 @@
       <c r="J49" s="8" t="n"/>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L49" s="9" t="n"/>
@@ -2434,7 +2434,7 @@
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L50" s="9" t="n"/>
@@ -2472,7 +2472,7 @@
       <c r="J51" s="8" t="n"/>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L51" s="9" t="n"/>
@@ -2510,7 +2510,7 @@
       <c r="J52" s="8" t="n"/>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L52" s="9" t="n"/>
@@ -2548,7 +2548,7 @@
       <c r="J53" s="8" t="n"/>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L53" s="9" t="n"/>
@@ -2586,7 +2586,7 @@
       <c r="J54" s="8" t="n"/>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L54" s="9" t="n"/>
@@ -2624,7 +2624,7 @@
       <c r="J55" s="8" t="n"/>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L55" s="9" t="n"/>
@@ -2662,7 +2662,7 @@
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L56" s="9" t="n"/>
@@ -2700,7 +2700,7 @@
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L57" s="9" t="n"/>
@@ -2738,7 +2738,7 @@
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L58" s="9" t="n"/>
@@ -2776,7 +2776,7 @@
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE; trigger 6.00 m (odometry)</t>
+          <t>ACTIVE; v = 0 at 8.00 m (odometry)</t>
         </is>
       </c>
       <c r="L59" s="9" t="n"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IMU + odometry</t>
+          <t>IMU + odometry; tape as T1</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Topics as available on the robot: /unilidar/imu (frame unilidar_imu, m/s²), /odom_raw, /cmd_vel. The IMU is mounted upside down (z ≈ −9.8 m/s² at rest) and rotated: robot forward is at 111° in the IMU x-y plane (measured 2026-10-30). Gravity and bias: the 2 s at-rest mean before each run is subtracted.</t>
+          <t>Topics as available on the robot: /unilidar/imu (frame unilidar_imu, m/s²), /odom_raw, /cmd_vel. The IMU is mounted upside down (z ≈ −9.8 m/s² at rest) and rotated: robot forward is at 111° in the IMU x-y plane (measured 2026-10-30). Gravity and bias: the 2 s at-rest mean before each run is subtracted. Endpoint: Δx, Δy at the 8 m line as in T1 (RUN LOG columns H, I).</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -4198,17 +4198,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tape stopping distance</t>
+          <t>Tape stopping distance (Δx past the 8 m line)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Trigger at 6.00 m of wheel odometry (logged time and position); start line and tape to the robot reference point at rest.</t>
+          <t>Stop command at 8.00 m of wheel odometry (logged time and position); 8.00 m line and centerline as in T1.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Stop distance = tape (start line → reference point at rest) − logged trigger odometry. Label ACTIVE / COAST; if the run was not steady at the trigger or has no reliable trigger, skip rather than invent data.</t>
+          <t>Δx, Δy at the reference point as in T1. Stop distance = (8.00 m + Δx) − logged stop-command odometry. Label ACTIVE / COAST; if the run was not steady before the stop or has no reliable stop command, skip rather than invent data.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4532,16 +4532,16 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Δx, Δy at 8 m line</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>≥ 7 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4570,16 +4570,16 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Δx, Δy at 8 m line</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>≥ 7 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4608,16 +4608,16 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Δx, Δy at 8 m line</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>≥ 7 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4647,17 +4647,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6.0 + braking</t>
+          <t>8.0 + braking</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>start line → rest</t>
+          <t>Δx, Δy at 8 m line</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4687,17 +4687,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6.0 + braking</t>
+          <t>8.0 + braking</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>start line → rest</t>
+          <t>Δx, Δy at 8 m line</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4727,17 +4727,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6.0 + braking</t>
+          <t>8.0 + braking</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>start line → rest</t>
+          <t>Δx, Δy at 8 m line</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6.0 + braking</t>
+          <t>8.0 + braking</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>start line → rest</t>
+          <t>Δx, Δy at 8 m line</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>≥ 11 m</t>
+          <t>≥ 12 m</t>
         </is>
       </c>
     </row>

--- a/docs/protocol/Astibot_Floor_Experimental_Test_Protocol_v4.xlsx
+++ b/docs/protocol/Astibot_Floor_Experimental_Test_Protocol_v4.xlsx
@@ -421,7 +421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v4 (2026-10-30): T1–T3 aligned with the automated RoverX runner (dockerfiles/roverx-tests, exact commands in sheet RUN COMMANDS). T4–T5 unchanged from v3.</t>
+          <t>v4 (2026-10-31): T1–T4 aligned with the automated RoverX runner (dockerfiles/roverx-tests, exact commands in sheet RUN COMMANDS). T5 unchanged from v3.</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>v_initial = 0.20 / 0.50 / 1.00 / 1.50 m/s; as T1 up to the 8.00 m line (accelerate at 0.50 m/s², cruise, ≥ 1.0 s at steady speed: wheel speed within 5 %); at 8.00 m of wheel odometry a sudden stop: v = 0 at once, held (stop mode ACTIVE).</t>
+          <t>v_initial = 0.20 / 0.50 / 1.00 / 1.50 m/s; as T1 up to the 8.00 m line but accelerating at 1.50 m/s² (cruise, ≥ 1.0 s at steady speed: wheel speed within 5 %); at 8.00 m of wheel odometry a sudden stop: v = 0 at once, held (stop mode ACTIVE).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>As T1 (alignment, logging before motion, robot preparation, independent runs) up to the 8.00 m line, without the slow-down: when wheel odometry reads 8.00 m the system issues v = 0 at once (ACTIVE: the motor controllers brake and hold zero) and logs the stop-command time and odometry position. After rest, tape Δx and Δy at the reference point as in T1: Δx is how far past the 8 m line the robot stopped. Stop distance = (8.00 m + Δx) − stop-command odometry (computed). COAST (wheel power cut at the line) only as a separate, labelled condition. A run not steady at the line is flagged (steady_ok = false) and repeated.</t>
+          <t>As T1 (alignment, logging before motion, robot preparation, independent runs) up to the 8.00 m line, accelerating at 1.50 m/s², without the slow-down: when wheel odometry reads 8.00 m the system issues v = 0 at once (ACTIVE: the motor controllers brake and hold zero) and logs the stop-command time and odometry position. After rest, tape Δx and Δy at the reference point as in T1: Δx is how far past the 8 m line the robot stopped. Stop distance = (8.00 m + Δx) − stop-command odometry (computed). COAST (wheel power cut at the line) only as a separate, labelled condition. A run not steady at the line is flagged (steady_ok = false) and repeated.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Fixed start point, sufficient free area</t>
+          <t>Fixed start point, sufficient free area: a clear circle of at least the robot's diagonal plus a margin. Same chassis pointers as T1 (front and rear centre); robot centre = their midpoint.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>yaw_rate=+0.30 / -0.30 / +0.60 / -0.60 rad/s; target ~90°</t>
+          <t>yaw_rate = +0.30 / −0.30 / +0.60 / −0.60 rad/s (+ = counter-clockwise, left); v = 0; turn rate ramped at 1.0 rad/s²; stop (v = 0, w = 0 at once) when the IMU heading has turned 90°.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Set v=0; issue angular rate until about 90° rotation (via display/IMU yaw or timed command), then stop. Do not need exact final heading. Record raw gyro and estimated heading; measure displacement of robot center if possible.</t>
+          <t>1) Robot at rest; mark the floor under both pointers. 2) Run the condition (RUN COMMANDS). The system starts IMU + odometry logging (bag) before motion, turns the lidar on, powers the wheels, stays still 2 s (gyro bias), turns at the yaw rate with v = 0 and stops when the bias-corrected IMU heading reaches 90°; it aborts if the heading moves against the command (wrong IMU sign), past 135°, or if the centre moves &gt; 0.5 m. 3) After rest, mark under both pointers again; tape the centre displacement (Δx along the original heading, Δy across). The final heading is not required to be exact: the overshoot is recorded.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Commanded yaw rate/direction, actual gyro z, estimated heading, center drift [cm], odometry + IMU paths, floor marks</t>
+          <t>Automatic: commanded yaw rate and direction, IMU gyro z (raw in bag; achieved cruise rate, ratio to command, peak, time to rate), IMU heading at stop and at rest (overshoot), wheel-odometry heading and its ratio to the IMU, wheel-odometry centre drift, odometry + IMU paths (bag). Manual: centre drift Δx, Δy [cm]; floor marks.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Skid-steer inherently scrubs wheels; do not equate turning marks with traction failure</t>
+          <t>Skid-steer inherently scrubs wheels; do not equate turning marks with traction failure Heading from the gyro, bias measured in the 2 s still period before each run.</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <row r="2" ht="32.1" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Enter tape measurements for every T1–T3 trial: Δx/Δy at the 8 m line (T3: stop distance = 8 m + Δx − stop-command odometry) • every executed trial logs raw IMU and odometry (bag) • trial ID = &lt;test&gt;_&lt;v|a&gt;&lt;setpoint&gt;_r&lt;repeat&gt;_&lt;HHMMSS&gt;, e.g. T1_v0.50_r3_101530</t>
+          <t>Enter tape measurements for every T1–T4 trial: Δx/Δy at the 8 m line (T4: robot-centre displacement) (T3: stop distance = 8 m + Δx − stop-command odometry) • every executed trial logs raw IMU and odometry (bag) • trial ID = &lt;test&gt;_&lt;v|a&gt;&lt;setpoint&gt;_r&lt;repeat&gt;_&lt;HHMMSS&gt;, e.g. T1_v0.50_r3_101530</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>0.2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0.2</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0.2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
         <v>0.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
         <v>0.5</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0.5</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0</v>
@@ -2304,7 +2304,7 @@
         <v>0.5</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>0.5</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         <v>0.5</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>0</v>
@@ -2570,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
         <v>1.5</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>1.5</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>1.5</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>0</v>
@@ -2722,7 +2722,7 @@
         <v>1.5</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>1.5</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>0</v>
@@ -2810,7 +2810,11 @@
       <c r="H60" s="8" t="n"/>
       <c r="I60" s="8" t="n"/>
       <c r="J60" s="8" t="n"/>
-      <c r="K60" s="10" t="n"/>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L60" s="9" t="n"/>
       <c r="M60" s="9" t="n"/>
       <c r="N60" s="10" t="n"/>
@@ -2842,7 +2846,11 @@
       <c r="H61" s="8" t="n"/>
       <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="n"/>
-      <c r="K61" s="7" t="n"/>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L61" s="9" t="n"/>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="7" t="n"/>
@@ -2874,7 +2882,11 @@
       <c r="H62" s="8" t="n"/>
       <c r="I62" s="8" t="n"/>
       <c r="J62" s="8" t="n"/>
-      <c r="K62" s="10" t="n"/>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L62" s="9" t="n"/>
       <c r="M62" s="9" t="n"/>
       <c r="N62" s="10" t="n"/>
@@ -2906,7 +2918,11 @@
       <c r="H63" s="8" t="n"/>
       <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n"/>
-      <c r="K63" s="7" t="n"/>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L63" s="9" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="7" t="n"/>
@@ -2938,7 +2954,11 @@
       <c r="H64" s="8" t="n"/>
       <c r="I64" s="8" t="n"/>
       <c r="J64" s="8" t="n"/>
-      <c r="K64" s="10" t="n"/>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L64" s="9" t="n"/>
       <c r="M64" s="9" t="n"/>
       <c r="N64" s="10" t="n"/>
@@ -2970,7 +2990,11 @@
       <c r="H65" s="8" t="n"/>
       <c r="I65" s="8" t="n"/>
       <c r="J65" s="8" t="n"/>
-      <c r="K65" s="7" t="n"/>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L65" s="9" t="n"/>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="7" t="n"/>
@@ -3002,7 +3026,11 @@
       <c r="H66" s="8" t="n"/>
       <c r="I66" s="8" t="n"/>
       <c r="J66" s="8" t="n"/>
-      <c r="K66" s="10" t="n"/>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L66" s="9" t="n"/>
       <c r="M66" s="9" t="n"/>
       <c r="N66" s="10" t="n"/>
@@ -3034,7 +3062,11 @@
       <c r="H67" s="8" t="n"/>
       <c r="I67" s="8" t="n"/>
       <c r="J67" s="8" t="n"/>
-      <c r="K67" s="7" t="n"/>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="7" t="n"/>
@@ -3066,7 +3098,11 @@
       <c r="H68" s="8" t="n"/>
       <c r="I68" s="8" t="n"/>
       <c r="J68" s="8" t="n"/>
-      <c r="K68" s="10" t="n"/>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L68" s="9" t="n"/>
       <c r="M68" s="9" t="n"/>
       <c r="N68" s="10" t="n"/>
@@ -3098,7 +3134,11 @@
       <c r="H69" s="8" t="n"/>
       <c r="I69" s="8" t="n"/>
       <c r="J69" s="8" t="n"/>
-      <c r="K69" s="7" t="n"/>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L69" s="9" t="n"/>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="7" t="n"/>
@@ -3130,7 +3170,11 @@
       <c r="H70" s="8" t="n"/>
       <c r="I70" s="8" t="n"/>
       <c r="J70" s="8" t="n"/>
-      <c r="K70" s="10" t="n"/>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L70" s="9" t="n"/>
       <c r="M70" s="9" t="n"/>
       <c r="N70" s="10" t="n"/>
@@ -3162,7 +3206,11 @@
       <c r="H71" s="8" t="n"/>
       <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
-      <c r="K71" s="7" t="n"/>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="7" t="n"/>
@@ -3194,7 +3242,11 @@
       <c r="H72" s="8" t="n"/>
       <c r="I72" s="8" t="n"/>
       <c r="J72" s="8" t="n"/>
-      <c r="K72" s="10" t="n"/>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L72" s="9" t="n"/>
       <c r="M72" s="9" t="n"/>
       <c r="N72" s="10" t="n"/>
@@ -3226,7 +3278,11 @@
       <c r="H73" s="8" t="n"/>
       <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="n"/>
-      <c r="K73" s="7" t="n"/>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="7" t="n"/>
@@ -3258,7 +3314,11 @@
       <c r="H74" s="8" t="n"/>
       <c r="I74" s="8" t="n"/>
       <c r="J74" s="8" t="n"/>
-      <c r="K74" s="10" t="n"/>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L74" s="9" t="n"/>
       <c r="M74" s="9" t="n"/>
       <c r="N74" s="10" t="n"/>
@@ -3290,7 +3350,11 @@
       <c r="H75" s="8" t="n"/>
       <c r="I75" s="8" t="n"/>
       <c r="J75" s="8" t="n"/>
-      <c r="K75" s="7" t="n"/>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="7" t="n"/>
@@ -3322,7 +3386,11 @@
       <c r="H76" s="8" t="n"/>
       <c r="I76" s="8" t="n"/>
       <c r="J76" s="8" t="n"/>
-      <c r="K76" s="10" t="n"/>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L76" s="9" t="n"/>
       <c r="M76" s="9" t="n"/>
       <c r="N76" s="10" t="n"/>
@@ -3354,7 +3422,11 @@
       <c r="H77" s="8" t="n"/>
       <c r="I77" s="8" t="n"/>
       <c r="J77" s="8" t="n"/>
-      <c r="K77" s="7" t="n"/>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="7" t="n"/>
@@ -3386,7 +3458,11 @@
       <c r="H78" s="8" t="n"/>
       <c r="I78" s="8" t="n"/>
       <c r="J78" s="8" t="n"/>
-      <c r="K78" s="10" t="n"/>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L78" s="9" t="n"/>
       <c r="M78" s="9" t="n"/>
       <c r="N78" s="10" t="n"/>
@@ -3418,7 +3494,11 @@
       <c r="H79" s="8" t="n"/>
       <c r="I79" s="8" t="n"/>
       <c r="J79" s="8" t="n"/>
-      <c r="K79" s="7" t="n"/>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>Stop at 90° (IMU heading)</t>
+        </is>
+      </c>
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="7" t="n"/>
@@ -4230,12 +4310,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Yaw rate sign and peak; approximate final yaw; manually observed translation of center.</t>
+          <t>Yaw rate sign and peak; approximate final yaw; manually observed translation of center. Streams: /unilidar/imu gyro z (sign: imu_z_sign = −1, IMU upside down), /odom_raw (wheel heading), /cmd_vel.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Wheel scrubbing is physically expected in turns.</t>
+          <t>Wheel scrubbing is physically expected in turns. Centre = midpoint of the two pointer marks; Δx along the original heading (+ forward), Δy across (+ left). Achieved rate is reported as measured (ratio to command), not judged against the command.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4286,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4302,7 +4382,7 @@
     <row r="1" ht="35.1" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>RUN COMMANDS | T1–T3 (RoverX automated runner)</t>
+          <t>RUN COMMANDS | T1–T4 (RoverX automated runner)</t>
         </is>
       </c>
     </row>
@@ -4778,6 +4858,166 @@
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>≥ 12 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="35.1" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>w = +0.30 rad/s</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>curl -s -X POST localhost:8090/t4 -d '{"yaw_rate": 0.3}' | jq</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>T4_w+0.30_r1_&lt;time&gt; … _r5_&lt;time&gt;</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>90° in place</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>centre Δx, Δy</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>free circle</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="35.1" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>w = -0.30 rad/s</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>curl -s -X POST localhost:8090/t4 -d '{"yaw_rate": -0.3}' | jq</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>T4_w-0.30_r1_&lt;time&gt; … _r5_&lt;time&gt;</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>90° in place</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>centre Δx, Δy</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>free circle</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="35.1" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>w = +0.60 rad/s</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>curl -s -X POST localhost:8090/t4 -d '{"yaw_rate": 0.6}' | jq</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>T4_w+0.60_r1_&lt;time&gt; … _r5_&lt;time&gt;</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>90° in place</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>centre Δx, Δy</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>free circle</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="35.1" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>w = -0.60 rad/s</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>curl -s -X POST localhost:8090/t4 -d '{"yaw_rate": -0.6}' | jq</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>T4_w-0.60_r1_&lt;time&gt; … _r5_&lt;time&gt;</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>90° in place</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>centre Δx, Δy</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>free circle</t>
         </is>
       </c>
     </row>
